--- a/docs/archive_project_database_template.xlsx
+++ b/docs/archive_project_database_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/OLIGNELAB/ONLINEPORTFOLIO/V1/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B384D7-68FF-D74B-8EC0-6D64050FFDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A44D6E-804C-BC42-BFC4-E40B6297C1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="123">
   <si>
     <t>id</t>
   </si>
@@ -383,6 +383,12 @@
   </si>
   <si>
     <t>toron, tissage, sauvegarde</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1235,7 +1241,7 @@
     <col min="7" max="7" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1257,8 +1263,11 @@
       <c r="G1" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1280,8 +1289,11 @@
       <c r="G2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1303,8 +1315,11 @@
       <c r="G3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1326,8 +1341,11 @@
       <c r="G4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1349,8 +1367,11 @@
       <c r="G5" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1372,8 +1393,11 @@
       <c r="G6" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -1395,8 +1419,11 @@
       <c r="G7" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -1418,8 +1445,11 @@
       <c r="G8" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -1441,8 +1471,11 @@
       <c r="G9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -1464,8 +1497,11 @@
       <c r="G10" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -1487,8 +1523,11 @@
       <c r="G11" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -1507,8 +1546,11 @@
       <c r="G12" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -1530,8 +1572,11 @@
       <c r="G13" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>74</v>
       </c>
@@ -1553,8 +1598,11 @@
       <c r="G14" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>103</v>
       </c>
@@ -1573,8 +1621,11 @@
       <c r="G15" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1593,8 +1644,11 @@
       <c r="G16" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1613,8 +1667,11 @@
       <c r="G17" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1636,8 +1693,11 @@
       <c r="G18" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1659,8 +1719,11 @@
       <c r="G19" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1679,8 +1742,11 @@
       <c r="G20" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1699,8 +1765,11 @@
       <c r="G21" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1719,8 +1788,11 @@
       <c r="G22" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -1742,8 +1814,11 @@
       <c r="G23" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1762,8 +1837,11 @@
       <c r="G24" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1785,8 +1863,11 @@
       <c r="G25" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1808,8 +1889,11 @@
       <c r="G26" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -1828,8 +1912,11 @@
       <c r="G27" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -1845,8 +1932,11 @@
       <c r="E28" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -1865,8 +1955,11 @@
       <c r="F29" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1884,6 +1977,14 @@
       </c>
       <c r="F30" t="s">
         <v>101</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
